--- a/AAAGameData/DataTables/Level/ObjectiveTable.xlsx
+++ b/AAAGameData/DataTables/Level/ObjectiveTable.xlsx
@@ -682,26 +682,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>研发一定数量科技</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ResearchTechnologyCount</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Objective.ResearchTechnologyCount</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="B15" t="n">
         <v>11</v>
@@ -959,26 +939,6 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>Objective.BuildProductionBuilding</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>建造科研建筑</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>BuildResearchBuilding</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Objective.BuildResearchBuilding</t>
         </is>
       </c>
     </row>
